--- a/data/trans_dic/P19F$mañana-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P19F$mañana-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se cepilla los dientes por la mañana</t>
+          <t>Población que, al menos, se cepilla los dientes por la mañana (tasa de respuesta: 93,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>38,93; 52,27</t>
+          <t>37,51; 51,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>38,73; 53,38</t>
+          <t>38,49; 52,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40,95; 50,71</t>
+          <t>40,7; 50,43</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>37,78; 48,57</t>
+          <t>37,92; 49,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>36,22; 48,49</t>
+          <t>36,35; 47,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38,7; 46,92</t>
+          <t>38,59; 46,54</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>32,67; 43,44</t>
+          <t>32,62; 42,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>38,9; 50,08</t>
+          <t>39,51; 50,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37,37; 45,2</t>
+          <t>37,52; 44,95</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>32,75; 44,19</t>
+          <t>32,52; 43,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>43,34; 54,66</t>
+          <t>44,01; 54,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39,62; 47,14</t>
+          <t>39,49; 47,74</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>36,93; 50,6</t>
+          <t>36,67; 50,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>42,06; 55,12</t>
+          <t>42,52; 54,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42,11; 51,54</t>
+          <t>41,82; 51,47</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>30,88; 45,68</t>
+          <t>29,96; 45,02</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>39,93; 54,94</t>
+          <t>39,32; 55,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>37,34; 47,74</t>
+          <t>37,57; 48,16</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>33,78; 50,62</t>
+          <t>33,8; 50,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>25,76; 41,85</t>
+          <t>26,21; 41,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31,62; 43,45</t>
+          <t>31,02; 42,62</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>38,66; 43,19</t>
+          <t>38,16; 43,07</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>42,51; 47,35</t>
+          <t>42,49; 47,53</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>41,32; 44,73</t>
+          <t>41,2; 44,52</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se cepilla los dientes por la mañana</t>
+          <t>Población que, al menos, se cepilla los dientes por la mañana (tasa de respuesta: 93,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>89184; 119734</t>
+          <t>85935; 117752</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>69041; 95167</t>
+          <t>68620; 94004</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>166826; 206548</t>
+          <t>165790; 205417</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>124020; 159412</t>
+          <t>124473; 161434</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>98448; 131789</t>
+          <t>98786; 129973</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>232202; 281552</t>
+          <t>231536; 279283</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>113556; 151003</t>
+          <t>113385; 148711</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>126778; 163191</t>
+          <t>128772; 165587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>251679; 304412</t>
+          <t>252706; 302716</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>111187; 150041</t>
+          <t>110423; 147756</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>143481; 180945</t>
+          <t>145684; 180846</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>265696; 316066</t>
+          <t>264807; 320150</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>86912; 119069</t>
+          <t>86297; 119769</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>110553; 144867</t>
+          <t>111744; 144327</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>209789; 256725</t>
+          <t>208338; 256410</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>53612; 79306</t>
+          <t>52015; 78151</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>73786; 101537</t>
+          <t>72662; 101955</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>133830; 171087</t>
+          <t>134656; 172603</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>42377; 63504</t>
+          <t>42408; 63031</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>48408; 78654</t>
+          <t>49254; 78161</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>99107; 136184</t>
+          <t>97204; 133576</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>687665; 768305</t>
+          <t>678823; 766106</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>740774; 825126</t>
+          <t>740350; 828265</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1455044; 1575069</t>
+          <t>1450680; 1567574</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19F$mañana-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P19F$mañana-Edad-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>37,51; 51,4</t>
+          <t>38,77; 51,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>38,49; 52,73</t>
+          <t>38,96; 53,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40,7; 50,43</t>
+          <t>40,51; 50,08</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>37,92; 49,18</t>
+          <t>37,44; 48,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>36,35; 47,82</t>
+          <t>36,42; 47,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38,59; 46,54</t>
+          <t>38,57; 46,52</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>32,62; 42,78</t>
+          <t>33,06; 43,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39,51; 50,81</t>
+          <t>38,58; 49,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37,52; 44,95</t>
+          <t>37,49; 45,12</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>32,52; 43,52</t>
+          <t>32,38; 44,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>44,01; 54,63</t>
+          <t>43,62; 54,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39,49; 47,74</t>
+          <t>39,39; 47,62</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>36,67; 50,89</t>
+          <t>37,13; 50,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>42,52; 54,92</t>
+          <t>41,76; 54,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41,82; 51,47</t>
+          <t>41,75; 50,91</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>29,96; 45,02</t>
+          <t>30,81; 45,16</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>39,32; 55,17</t>
+          <t>39,96; 54,93</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>37,57; 48,16</t>
+          <t>37,38; 47,51</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>33,8; 50,24</t>
+          <t>34,59; 49,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>26,21; 41,59</t>
+          <t>26,35; 41,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31,02; 42,62</t>
+          <t>31,25; 42,94</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>38,16; 43,07</t>
+          <t>38,71; 43,42</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>42,49; 47,53</t>
+          <t>42,57; 47,49</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>41,2; 44,52</t>
+          <t>41,2; 44,45</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>85935; 117752</t>
+          <t>88807; 118659</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>68620; 94004</t>
+          <t>69450; 94527</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>165790; 205417</t>
+          <t>165022; 203982</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>124473; 161434</t>
+          <t>122881; 158824</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>98786; 129973</t>
+          <t>98985; 130387</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>231536; 279283</t>
+          <t>231409; 279120</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>113385; 148711</t>
+          <t>114923; 150432</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>128772; 165587</t>
+          <t>125743; 161276</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>252706; 302716</t>
+          <t>252509; 303853</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>110423; 147756</t>
+          <t>109950; 149407</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>145684; 180846</t>
+          <t>144408; 180340</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>264807; 320150</t>
+          <t>264141; 319285</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>86297; 119769</t>
+          <t>87376; 119948</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>111744; 144327</t>
+          <t>109747; 144481</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>208338; 256410</t>
+          <t>207985; 253618</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>52015; 78151</t>
+          <t>53488; 78394</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>72662; 101955</t>
+          <t>73845; 101504</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>134656; 172603</t>
+          <t>133979; 170287</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>42408; 63031</t>
+          <t>43391; 62364</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>49254; 78161</t>
+          <t>49516; 77828</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>97204; 133576</t>
+          <t>97941; 134565</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>678823; 766106</t>
+          <t>688651; 772357</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>740350; 828265</t>
+          <t>741817; 827572</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1450680; 1567574</t>
+          <t>1450668; 1565117</t>
         </is>
       </c>
     </row>
